--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484174_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484174_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9092</v>
+        <v>5.2064</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9224</v>
+        <v>2.7807</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9868</v>
+        <v>2.4257</v>
       </c>
       <c r="G2" t="n">
         <v>2.7534</v>
@@ -610,13 +610,13 @@
         <v>2.7774</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2073</v>
+        <v>0.5044</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5216</v>
+        <v>0.3799</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6857</v>
+        <v>0.1245</v>
       </c>
       <c r="V2" t="n">
         <v>2.1469</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7255</v>
+        <v>5.0681</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4187</v>
+        <v>7.0139</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6932</v>
+        <v>-1.9457</v>
       </c>
       <c r="G3" t="n">
         <v>-0.5584</v>
@@ -688,13 +688,13 @@
         <v>2.9758</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.004</v>
+        <v>0.3387</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1586</v>
+        <v>0.4366</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1546</v>
+        <v>-0.0979</v>
       </c>
       <c r="V3" t="n">
         <v>3.304</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6232</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3854</v>
+        <v>1.3684</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7622</v>
+        <v>-0.6219</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0659</v>
@@ -766,13 +766,13 @@
         <v>2.3806</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5357</v>
+        <v>0.6589</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5103</v>
+        <v>0.4932</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0254</v>
+        <v>0.1657</v>
       </c>
       <c r="V4" t="n">
         <v>0.7486</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CAMPENY LLOVERAS</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3892</v>
+        <v>0.4224</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0999</v>
+        <v>0.3858</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4891</v>
+        <v>0.0365</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9941</v>
+        <v>0.5078</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6753</v>
+        <v>1.819</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3187</v>
+        <v>-1.3112</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9923</v>
+        <v>-0.6672</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3523</v>
+        <v>1.3307</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.64</v>
+        <v>-1.9979</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9864</v>
+        <v>1.175</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0276</v>
+        <v>0.4883</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9588</v>
+        <v>0.6867</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5952</v>
+        <v>0.5952</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2562</v>
+        <v>-0.9466</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8843</v>
+        <v>-0.4194</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6281</v>
+        <v>-0.5272</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.266</v>
+        <v>0.266</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.266</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. KOHAN LÓPEZ</t>
+          <t>J. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3345</v>
+        <v>0.2945</v>
       </c>
       <c r="E6" t="n">
-        <v>0.638</v>
+        <v>-1.5874</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3036</v>
+        <v>1.8819</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0454</v>
+        <v>0.9941</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1815</v>
+        <v>0.6753</v>
       </c>
       <c r="I6" t="n">
-        <v>0.136</v>
+        <v>0.3187</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0202</v>
+        <v>-0.9923</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0202</v>
+        <v>-0.3523</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.64</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.06560000000000001</v>
+        <v>1.9864</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2016</v>
+        <v>1.0276</v>
       </c>
       <c r="O6" t="n">
-        <v>0.136</v>
+        <v>0.9588</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.3968</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.1615</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6178</v>
+        <v>0.3968</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1173</v>
+        <v>-0.2353</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1206</v>
+        <v>-0.266</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1206</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1184</v>
+        <v>0.1185</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1818</v>
+        <v>1.8214</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3001</v>
+        <v>-1.7029</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5078</v>
+        <v>0.1382</v>
       </c>
       <c r="H7" t="n">
-        <v>1.819</v>
+        <v>-0.6042</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3112</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6672</v>
+        <v>2.576</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3307</v>
+        <v>0.5252</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.9979</v>
+        <v>2.0508</v>
       </c>
       <c r="M7" t="n">
-        <v>1.175</v>
+        <v>-2.4378</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4883</v>
+        <v>-1.1295</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6867</v>
+        <v>-1.3084</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5952</v>
+        <v>1.9838</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4873</v>
+        <v>0.3868</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.3799</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8639</v>
+        <v>0.007</v>
       </c>
       <c r="V7" t="n">
-        <v>0.266</v>
+        <v>-1.3984</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4724</v>
+        <v>-0.1425</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2065</v>
+        <v>-1.2558</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BLÁZQUEZ FARRIOL</t>
+          <t>T. KOHAN LÓPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3961</v>
+        <v>-0.0456</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0496</v>
+        <v>0.2299</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4458</v>
+        <v>-0.2755</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6337</v>
+        <v>-0.0454</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6804</v>
+        <v>-0.1815</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0467</v>
+        <v>0.136</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5795</v>
+        <v>0.0202</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6197</v>
+        <v>0.0202</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0542</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0607</v>
+        <v>-0.2016</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0065</v>
+        <v>0.136</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1984</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1984</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1599</v>
+        <v>0.1205</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6292</v>
+        <v>0.2097</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4693</v>
+        <v>-0.0893</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1206</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>A. BLÁZQUEZ FARRIOL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9026</v>
+        <v>-0.59</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7161</v>
+        <v>-0.2564</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6187</v>
+        <v>-0.3336</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1382</v>
+        <v>-0.6337</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6042</v>
+        <v>-0.6804</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.0467</v>
       </c>
       <c r="J9" t="n">
-        <v>2.576</v>
+        <v>-0.5795</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5252</v>
+        <v>-0.6197</v>
       </c>
       <c r="L9" t="n">
-        <v>2.0508</v>
+        <v>0.0402</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.4378</v>
+        <v>-0.0542</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1295</v>
+        <v>-0.0607</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3084</v>
+        <v>0.0065</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9919</v>
+        <v>0.1984</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9838</v>
+        <v>0.1984</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6343</v>
+        <v>-0.034</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7254</v>
+        <v>0.3231</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0911</v>
+        <v>-0.3571</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3984</v>
+        <v>-0.1206</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1425</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2558</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0422</v>
+        <v>-1.0626</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6307</v>
+        <v>-0.4266</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4115</v>
+        <v>-0.636</v>
       </c>
       <c r="G10" t="n">
         <v>0.2285</v>
@@ -1234,13 +1234,13 @@
         <v>0.1984</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0034</v>
+        <v>-0.017</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.238</v>
+        <v>-0.034</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2414</v>
+        <v>0.017</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4724</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4147</v>
+        <v>-1.7925</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.7313</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8648</v>
+        <v>-1.0612</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1988</v>
@@ -1312,13 +1312,13 @@
         <v>0.7935</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0176</v>
+        <v>-0.3954</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0679</v>
+        <v>-0.2493</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0504</v>
+        <v>-0.146</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9541</v>
+        <v>-2.2771</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1143</v>
+        <v>-0.7459</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8398</v>
+        <v>-1.5312</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7919</v>
@@ -1390,13 +1390,13 @@
         <v>2.579</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8882</v>
+        <v>-0.2111</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2436</v>
+        <v>0.1248</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6445</v>
+        <v>-0.3359</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8692</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.153500000000001</v>
+        <v>6.0886</v>
       </c>
       <c r="E13" t="n">
-        <v>8.917199999999998</v>
+        <v>9.852499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.7638</v>
+        <v>-3.7639</v>
       </c>
       <c r="G13" t="n">
         <v>0.3278999999999996</v>
@@ -1438,7 +1438,7 @@
         <v>3.0486</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.7209</v>
+        <v>-2.720899999999999</v>
       </c>
       <c r="J13" t="n">
         <v>10.0105</v>
@@ -1447,7 +1447,7 @@
         <v>5.5741</v>
       </c>
       <c r="L13" t="n">
-        <v>4.436299999999999</v>
+        <v>4.4363</v>
       </c>
       <c r="M13" t="n">
         <v>-9.682600000000001</v>
@@ -1468,16 +1468,16 @@
         <v>14.8789</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3683999999999999</v>
+        <v>0.5667</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1062</v>
+        <v>2.0413</v>
       </c>
       <c r="U13" t="n">
         <v>-1.4745</v>
       </c>
       <c r="V13" t="n">
-        <v>2.218299999999999</v>
+        <v>2.218300000000001</v>
       </c>
       <c r="W13" t="n">
         <v>9.703899999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0529</v>
+        <v>6.3716</v>
       </c>
       <c r="E14" t="n">
-        <v>7.4851</v>
+        <v>8.199299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4322</v>
+        <v>-1.8277</v>
       </c>
       <c r="G14" t="n">
         <v>3.9546</v>
@@ -1546,13 +1546,13 @@
         <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9857</v>
+        <v>0.333</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3683</v>
+        <v>0.3459</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.0129</v>
       </c>
       <c r="V14" t="n">
         <v>0.6954</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.264</v>
+        <v>2.1713</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3306</v>
+        <v>0.3657</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0665</v>
+        <v>1.8057</v>
       </c>
       <c r="G15" t="n">
-        <v>1.589</v>
+        <v>0.237</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.6802</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7074</v>
+        <v>-0.4432</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8859</v>
+        <v>0.6636</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6734</v>
+        <v>0.7311</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2125</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.297</v>
+        <v>-0.4265</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.0509</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5051</v>
+        <v>-0.3756</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7935</v>
+        <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.3146</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2301</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3566</v>
+        <v>0.2238</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.4294</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2065</v>
+        <v>0.6032</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2065</v>
+        <v>-0.1738</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9385</v>
+        <v>1.7377</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4506</v>
+        <v>3.6164</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3891</v>
+        <v>-1.8786</v>
       </c>
       <c r="G16" t="n">
-        <v>0.237</v>
+        <v>1.589</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6802</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4432</v>
+        <v>0.7074</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6636</v>
+        <v>2.8859</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7311</v>
+        <v>1.6734</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.06759999999999999</v>
+        <v>1.2125</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4265</v>
+        <v>-1.297</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0509</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3756</v>
+        <v>-0.5051</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1903</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1822</v>
+        <v>0.7935</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9182</v>
+        <v>0.3472</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7254</v>
+        <v>0.5159</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1928</v>
+        <v>-0.1687</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4294</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6032</v>
+        <v>1.2065</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1738</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2689</v>
+        <v>0.711</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4441</v>
+        <v>-0.138</v>
       </c>
       <c r="F17" t="n">
-        <v>0.713</v>
+        <v>0.8491</v>
       </c>
       <c r="G17" t="n">
         <v>0.7332</v>
@@ -1780,13 +1780,13 @@
         <v>0.7935</v>
       </c>
       <c r="S17" t="n">
-        <v>-0</v>
+        <v>0.4421</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.238</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.238</v>
+        <v>0.3741</v>
       </c>
       <c r="V17" t="n">
         <v>-0.266</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2893</v>
+        <v>-0.781</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8089</v>
+        <v>-0.1945</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5196</v>
+        <v>-0.5866</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2988</v>
+        <v>-0.449</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2496</v>
+        <v>-1.1694</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0492</v>
+        <v>0.7204</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2397</v>
+        <v>0.6051</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3201</v>
+        <v>-0.6399</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0803</v>
+        <v>1.245</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0591</v>
+        <v>-1.0542</v>
       </c>
       <c r="N18" t="n">
-        <v>0.07049999999999999</v>
+        <v>-0.5295</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1295</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3968</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6127</v>
+        <v>-0.2012</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4308</v>
+        <v>-0.0737</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1819</v>
+        <v>-0.1276</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0514</v>
+        <v>-0.7816</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2965</v>
+        <v>-1.217</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7549</v>
+        <v>0.4354</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.449</v>
+        <v>-1.2988</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1694</v>
+        <v>-1.2496</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7204</v>
+        <v>-0.0492</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6051</v>
+        <v>-1.2397</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6399</v>
+        <v>-1.3201</v>
       </c>
       <c r="L19" t="n">
-        <v>1.245</v>
+        <v>0.0803</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0542</v>
+        <v>-0.0591</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5295</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.1295</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3968</v>
+        <v>0.3968</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4716</v>
+        <v>0.1205</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1757</v>
+        <v>0.0227</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2959</v>
+        <v>0.0978</v>
       </c>
       <c r="V19" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3213</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6079</v>
+        <v>-2.4038</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2866</v>
+        <v>1.5264</v>
       </c>
       <c r="G20" t="n">
         <v>-3.1105</v>
@@ -2014,13 +2014,13 @@
         <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3355</v>
+        <v>0.7794</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3232</v>
+        <v>0.5273</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0123</v>
+        <v>0.2521</v>
       </c>
       <c r="V20" t="n">
         <v>2.8423</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6584</v>
+        <v>-1.9348</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7271</v>
+        <v>-0.9665</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3855</v>
+        <v>-0.9684</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3741</v>
+        <v>-0.6963</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6248</v>
+        <v>-0.4438</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9989</v>
+        <v>-0.2526</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4185</v>
+        <v>0.0202</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8434</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0444</v>
+        <v>-0.7165</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1999</v>
+        <v>-0.4639</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1555</v>
+        <v>-0.2526</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1903</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8962</v>
+        <v>-0.1077</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2924</v>
+        <v>-0.2607</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3963</v>
+        <v>0.153</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.7384</v>
+        <v>-0.3373</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7384</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8124</v>
+        <v>-2.3888</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0685</v>
+        <v>-0.1911</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7439</v>
+        <v>-2.1976</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6963</v>
+        <v>0.3741</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4438</v>
+        <v>-0.6248</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2526</v>
+        <v>0.9989</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0202</v>
+        <v>1.4185</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0202</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="L22" t="n">
+        <v>0.8434</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1.0444</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1.1999</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.1555</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-1.1903</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.9838</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.7935</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.2084</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-1.7384</v>
+      </c>
+      <c r="W22" t="n">
         <v>0</v>
       </c>
-      <c r="M22" t="n">
-        <v>-0.7165</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-0.4639</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-0.2526</v>
-      </c>
-      <c r="P22" t="n">
-        <v>-0.7935</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-0.9919</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.1984</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.0147</v>
-      </c>
-      <c r="T22" t="n">
-        <v>-0.3627</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.3774</v>
-      </c>
-      <c r="V22" t="n">
-        <v>-0.3373</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.266</v>
-      </c>
       <c r="X22" t="n">
-        <v>-0.6032</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3739</v>
+        <v>-3.5482</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5427</v>
+        <v>0.2366</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.9166</v>
+        <v>-3.7848</v>
       </c>
       <c r="G23" t="n">
         <v>0.6453</v>
@@ -2248,13 +2248,13 @@
         <v>1.3887</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0312</v>
+        <v>-0.1431</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0511</v>
+        <v>-0.2549</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.02</v>
+        <v>0.1118</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4633</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.171</v>
+        <v>-3.7926</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6451</v>
+        <v>-3.543</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5259</v>
+        <v>-0.2496</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3065</v>
@@ -2326,13 +2326,13 @@
         <v>1.7855</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0198</v>
+        <v>0.3585</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0171</v>
+        <v>0.1191</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0369</v>
+        <v>0.2394</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6463</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.1534</v>
+        <v>-3.1129</v>
       </c>
       <c r="E25" t="n">
-        <v>3.763899999999999</v>
+        <v>3.7641</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.917199999999999</v>
+        <v>-6.8767</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3279000000000007</v>
+        <v>-0.3279000000000003</v>
       </c>
       <c r="H25" t="n">
         <v>-3.0487</v>
@@ -2377,7 +2377,7 @@
         <v>2.720899999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>9.682500000000003</v>
+        <v>9.682499999999999</v>
       </c>
       <c r="K25" t="n">
         <v>2.525200000000001</v>
@@ -2389,7 +2389,7 @@
         <v>-10.0104</v>
       </c>
       <c r="N25" t="n">
-        <v>-5.5739</v>
+        <v>-5.573900000000001</v>
       </c>
       <c r="O25" t="n">
         <v>-4.436400000000001</v>
@@ -2404,13 +2404,13 @@
         <v>11.9031</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3685</v>
+        <v>2.4091</v>
       </c>
       <c r="T25" t="n">
-        <v>1.474599999999999</v>
+        <v>1.4747</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.1063</v>
+        <v>0.9344000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-2.2182</v>
@@ -2419,7 +2419,7 @@
         <v>7.4858</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.703800000000001</v>
+        <v>-9.703799999999999</v>
       </c>
     </row>
   </sheetData>
